--- a/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/项目统计导出模板.xlsx
+++ b/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/项目统计导出模板.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>{{title}}</t>
   </si>
@@ -71,6 +71,9 @@
     <t>项目助理</t>
   </si>
   <si>
+    <t>发布人</t>
+  </si>
+  <si>
     <t>操作人</t>
   </si>
   <si>
@@ -111,6 +114,9 @@
   </si>
   <si>
     <t>t.t13</t>
+  </si>
+  <si>
+    <t>t.t15</t>
   </si>
   <si>
     <t>t.t14}}</t>
@@ -126,7 +132,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,12 +146,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -158,18 +164,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -649,19 +643,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -670,151 +673,139 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1164,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -1176,119 +1167,126 @@
     <col min="10" max="10" width="18.125" customWidth="1"/>
     <col min="11" max="11" width="13.625" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
-    <col min="13" max="13" width="15.75" customWidth="1"/>
-    <col min="14" max="14" width="26.25" customWidth="1"/>
+    <col min="13" max="14" width="15.75" customWidth="1"/>
+    <col min="15" max="15" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:14">
+    <row r="1" ht="18.75" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" ht="14.25" spans="1:14">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="14.25" spans="1:15">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="M3" s="6" t="s">
         <v>28</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
